--- a/Analysis/Sensitivity_alpha_sweep_gemini.xlsx
+++ b/Analysis/Sensitivity_alpha_sweep_gemini.xlsx
@@ -491,16 +491,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.17606</v>
+        <v>0.17878</v>
       </c>
       <c r="G2" t="n">
-        <v>0.17334</v>
+        <v>0.18358</v>
       </c>
       <c r="H2" t="n">
-        <v>0.36206</v>
+        <v>0.39792</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6974400000000001</v>
+        <v>0.7025400000000001</v>
       </c>
       <c r="J2" t="n">
         <v>195</v>
@@ -529,19 +529,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.30986</v>
+        <v>0.29846</v>
       </c>
       <c r="G3" t="n">
-        <v>0.328</v>
+        <v>0.32102</v>
       </c>
       <c r="H3" t="n">
-        <v>0.48708</v>
+        <v>0.4748599999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>0.79582</v>
+        <v>0.7712800000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4">
@@ -567,16 +567,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.9234399999999999</v>
+        <v>0.8912800000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9348599999999999</v>
+        <v>0.9077</v>
       </c>
       <c r="H4" t="n">
-        <v>0.93126</v>
+        <v>0.90154</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9846</v>
+        <v>0.9795</v>
       </c>
       <c r="J4" t="n">
         <v>195</v>
@@ -607,16 +607,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.17538</v>
+        <v>0.11386</v>
       </c>
       <c r="G5" t="n">
-        <v>0.16924</v>
+        <v>0.11846</v>
       </c>
       <c r="H5" t="n">
-        <v>0.37334</v>
+        <v>0.3641</v>
       </c>
       <c r="I5" t="n">
-        <v>0.69336</v>
+        <v>0.6718200000000001</v>
       </c>
       <c r="J5" t="n">
         <v>195</v>
@@ -647,19 +647,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.30368</v>
+        <v>0.25674</v>
       </c>
       <c r="G6" t="n">
-        <v>0.31402</v>
+        <v>0.27642</v>
       </c>
       <c r="H6" t="n">
-        <v>0.47778</v>
+        <v>0.4594799999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7855000000000001</v>
+        <v>0.74666</v>
       </c>
       <c r="J6" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="7">
@@ -687,16 +687,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.91314</v>
+        <v>0.86324</v>
       </c>
       <c r="G7" t="n">
-        <v>0.92716</v>
+        <v>0.88412</v>
       </c>
       <c r="H7" t="n">
-        <v>0.92616</v>
+        <v>0.88208</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9897</v>
+        <v>0.9784799999999999</v>
       </c>
       <c r="J7" t="n">
         <v>195</v>
@@ -727,16 +727,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.17948</v>
+        <v>0.17538</v>
       </c>
       <c r="G8" t="n">
-        <v>0.17794</v>
+        <v>0.18104</v>
       </c>
       <c r="H8" t="n">
-        <v>0.36716</v>
+        <v>0.3928199999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.70152</v>
+        <v>0.7025400000000001</v>
       </c>
       <c r="J8" t="n">
         <v>195</v>
@@ -767,19 +767,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.31334</v>
+        <v>0.29642</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3306</v>
+        <v>0.32002</v>
       </c>
       <c r="H9" t="n">
-        <v>0.49224</v>
+        <v>0.4718</v>
       </c>
       <c r="I9" t="n">
-        <v>0.79582</v>
+        <v>0.7723</v>
       </c>
       <c r="J9" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10">
@@ -807,16 +807,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.92684</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9400000000000001</v>
+        <v>0.91028</v>
       </c>
       <c r="H10" t="n">
-        <v>0.93642</v>
+        <v>0.90668</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9897</v>
+        <v>0.9795</v>
       </c>
       <c r="J10" t="n">
         <v>195</v>
@@ -847,16 +847,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.17948</v>
+        <v>0.1829</v>
       </c>
       <c r="G11" t="n">
-        <v>0.17588</v>
+        <v>0.18922</v>
       </c>
       <c r="H11" t="n">
-        <v>0.36716</v>
+        <v>0.39898</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6974400000000001</v>
+        <v>0.7025400000000001</v>
       </c>
       <c r="J11" t="n">
         <v>195</v>
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.31334</v>
+        <v>0.30392</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3306</v>
+        <v>0.3277</v>
       </c>
       <c r="H12" t="n">
-        <v>0.49224</v>
+        <v>0.4779600000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.79582</v>
+        <v>0.7712800000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="13">
@@ -927,16 +927,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.92684</v>
+        <v>0.8912800000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9400000000000001</v>
+        <v>0.91028</v>
       </c>
       <c r="H13" t="n">
-        <v>0.93642</v>
+        <v>0.90668</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9897</v>
+        <v>0.9846</v>
       </c>
       <c r="J13" t="n">
         <v>195</v>
@@ -967,16 +967,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.18016</v>
+        <v>0.19658</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1759</v>
+        <v>0.20308</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3723</v>
+        <v>0.40614</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6974400000000001</v>
+        <v>0.7179400000000001</v>
       </c>
       <c r="J14" t="n">
         <v>195</v>
@@ -1007,19 +1007,19 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0.30986</v>
+        <v>0.3107799999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3254</v>
+        <v>0.33488</v>
       </c>
       <c r="H15" t="n">
-        <v>0.48708</v>
+        <v>0.4779600000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>0.79582</v>
+        <v>0.7805199999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="16">
@@ -1047,16 +1047,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.91654</v>
+        <v>0.8926399999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9323</v>
+        <v>0.9092399999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>0.93126</v>
+        <v>0.90668</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9897</v>
+        <v>0.9795</v>
       </c>
       <c r="J16" t="n">
         <v>195</v>
